--- a/preview/pr-13/CodeSystem-pcor-item-dictionary.xlsx
+++ b/preview/pr-13/CodeSystem-pcor-item-dictionary.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
